--- a/OpenSesame-local/mbrt_files/Instructions.xlsx
+++ b/OpenSesame-local/mbrt_files/Instructions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdabb12e9f34f4c5/10_Paper/105_MIA/10_BAS_Collab/MBRT/OpenSesame-local/mbrt_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{F025FCA2-9408-45A5-9FA0-E710623A8AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE274A7E-02C0-4FA6-A985-46608DDAE90A}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{F025FCA2-9408-45A5-9FA0-E710623A8AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E82F4C62-86FC-48C1-BB44-A2A50720789E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3128DB0A-6163-4D40-98DA-1667AB584357}"/>
+    <workbookView xWindow="37739" yWindow="380" windowWidth="26083" windowHeight="13830" xr2:uid="{3128DB0A-6163-4D40-98DA-1667AB584357}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>EN</t>
   </si>
@@ -60,9 +61,6 @@
   </si>
   <si>
     <t>end_pract_msg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dies ist das Ende der Übungsdurchgänge. </t>
   </si>
   <si>
     <t>instr_msg1a</t>
@@ -136,6 +134,75 @@
   </si>
   <si>
     <t>Die nun folgenden Stimuli werden Ihnen &lt;b&gt;teilweise gedreht präsentiert&lt;/b&gt;. Dies soll keinen Einfluss auf Ihre&lt;br&gt;Entscheidung haben. Sie sollen ausschließlich beurteilen, ob es sich um ein rechtes oder linkes Körperteil handelt.&lt;br&gt;&lt;br&gt;Entscheiden Sie bitte so &lt;b&gt;schnell und korrekt&lt;/b&gt; wie möglich.&lt;br&gt;&lt;br&gt;Wenn ein &lt;b&gt;linkes Körperteil&lt;/b&gt; (Arm oder Bein) abgespreizt ist, drücken Sie bitte die Taste &lt;b&gt;S&lt;/b&gt;.&lt;br&gt;Wenn ein &lt;b&gt;rechtes Körperteil&lt;/b&gt; (Arm oder Bein) abgespreizt ist, drücken Sie bitte die Taste &lt;b&gt;L&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>A continuación verá este tipo de estímulos.</t>
+  </si>
+  <si>
+    <t>Dans ce qui suit, vous verrez de tels stimuli.</t>
+  </si>
+  <si>
+    <t>Decida por favor tan &lt;b&gt;rápido y correctamente&lt;/b&gt; como sea posible si el&lt;br&gt;miembro apartado del cuerpo (brazo o pierna) es izquierdo o derecho, &lt;span style='color:orange'&gt;&lt;b&gt;poniéndose&lt;br&gt;en la perspectiva y la posición corporal de la persona representada.&lt;/span&gt;&lt;/b&gt;&lt;br&gt;&lt;br&gt;&lt;span style='color:orange'&gt;Imagínese cómo se &lt;b&gt;ve&lt;/b&gt; y cómo se &lt;b&gt;siente&lt;/b&gt; girarse usted mismo y apartar del cuerpo el&lt;br&gt;miembro correspondiente.&lt;/span&gt;&lt;br&gt;&lt;br&gt;Coloque su dedo índice izquierdo sobre la tecla &lt;b&gt;S&lt;/b&gt; y su dedo índice derecho sobre la tecla &lt;b&gt;L&lt;/b&gt;.&lt;br&gt;&lt;br&gt;Mantenga sus manos en esta posición y muévase lo menos posible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;miembro izquierdo&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;S&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;miembro derecho&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;L&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Veuillez décider aussi &lt;b&gt;rapidement et correctement&lt;/b&gt; que possible si le&lt;br&gt;membre écarté du corps (bras ou jambe) est gauche ou droit, &lt;span style='color:orange'&gt;&lt;b&gt;en vous plaçant&lt;br&gt;dans la perspective et la position corporelle de la personne représentée.&lt;/span&gt;&lt;/b&gt;&lt;br&gt;&lt;br&gt;&lt;span style='color:orange'&gt;Imaginez à quoi cela &lt;b&gt;ressemble&lt;/b&gt; et ce que l'on &lt;b&gt;ressent&lt;/b&gt; lorsqu'on se tourne soi-même et que l'on écarte du corps le&lt;br&gt;membre correspondant.&lt;/span&gt;&lt;br&gt;&lt;br&gt;Placez votre index gauche sur la touche &lt;b&gt;S&lt;/b&gt; et votre index droit sur la touche &lt;b&gt;L&lt;/b&gt;.&lt;br&gt;&lt;br&gt;Gardez vos mains dans cette position et bougez le moins possible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;membre gauche&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;S&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;membre droit&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;L&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Decida por favor tan &lt;b&gt;rápido y correctamente&lt;/b&gt; como sea posible si el&lt;br&gt;miembro apartado del cuerpo (brazo o pierna) es izquierdo o derecho, &lt;span style='color:orange'&gt;&lt;b&gt;poniéndose&lt;br&gt;en la perspectiva y la posición corporal de la persona representada.&lt;/span&gt;&lt;/b&gt;&lt;br&gt;&lt;br&gt;&lt;span style='color:orange'&gt;Imagínese cómo se &lt;b&gt;ve&lt;/b&gt; y cómo se &lt;b&gt;siente&lt;/b&gt; girarse usted mismo y apartar del cuerpo el&lt;br&gt;miembro correspondiente.&lt;/span&gt;&lt;br&gt;&lt;br&gt;Coloque el dedo medio de su mano izquierda sobre la tecla &lt;b&gt;G&lt;/b&gt; y el dedo índice de su mano izquierda sobre la tecla &lt;b&gt;H&lt;/b&gt;.&lt;br&gt;Mantenga sus dedos en esta posición y muévase lo menos posible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;miembro izquierdo&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;G&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;miembro derecho&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;H&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Veuillez décider aussi &lt;b&gt;rapidement et correctement&lt;/b&gt; que possible si le&lt;br&gt;membre écarté du corps (bras ou jambe) est gauche ou droit, &lt;span style='color:orange'&gt;&lt;b&gt;en vous plaçant&lt;br&gt;dans la perspective et la position corporelle de la personne représentée.&lt;/span&gt;&lt;/b&gt;&lt;br&gt;&lt;br&gt;&lt;span style='color:orange'&gt;Imaginez à quoi cela &lt;b&gt;ressemble&lt;/b&gt; et ce que l'on &lt;b&gt;ressent&lt;/b&gt; lorsqu'on se tourne soi-même et que l'on écarte du corps le&lt;br&gt;membre correspondant.&lt;/span&gt;&lt;br&gt;&lt;br&gt;Placez le majeur de votre main gauche sur la touche &lt;b&gt;G&lt;/b&gt; et l'index de votre main gauche sur la touche &lt;b&gt;H&lt;/b&gt;.&lt;br&gt;Gardez vos doigts dans cette position et bougez le moins possible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;membre gauche&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;G&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;membre droit&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;H&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Decida por favor tan &lt;b&gt;rápido y correctamente&lt;/b&gt; como sea posible si el&lt;br&gt;miembro apartado del cuerpo (brazo o pierna) es izquierdo o derecho, &lt;span style='color:orange'&gt;&lt;b&gt;poniéndose&lt;br&gt;en la perspectiva y la posición corporal de la persona representada.&lt;/span&gt;&lt;/b&gt;&lt;br&gt;&lt;br&gt;&lt;span style='color:orange'&gt;Imagínese cómo se &lt;b&gt;ve&lt;/b&gt; y cómo se &lt;b&gt;siente&lt;/b&gt; girarse usted mismo y apartar del cuerpo el&lt;br&gt;miembro correspondiente.&lt;/span&gt;&lt;br&gt;&lt;br&gt;Coloque el dedo índice de su mano derecha sobre la tecla &lt;b&gt;G&lt;/b&gt; y el dedo medio de su mano derecha sobre la tecla &lt;b&gt;H&lt;/b&gt;.&lt;br&gt;Mantenga sus dedos en esta posición y muévase lo menos posible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;miembro izquierdo&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;G&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;miembro derecho&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;H&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Veuillez décider aussi &lt;b&gt;rapidement et correctement&lt;/b&gt; que possible si le&lt;br&gt;membre écarté du corps (bras ou jambe) est gauche ou droit, &lt;span style='color:orange'&gt;&lt;b&gt;en vous plaçant&lt;br&gt;dans la perspective et la position corporelle de la personne représentée.&lt;/span&gt;&lt;/b&gt;&lt;br&gt;&lt;br&gt;&lt;span style='color:orange'&gt;Imaginez à quoi cela &lt;b&gt;ressemble&lt;/b&gt; et ce que l'on &lt;b&gt;ressent&lt;/b&gt; lorsqu'on se tourne soi-même et que l'on écarte du corps le&lt;br&gt;membre correspondant.&lt;/span&gt;&lt;br&gt;&lt;br&gt;Placez l'index de votre main droite sur la touche &lt;b&gt;G&lt;/b&gt; et le majeur de votre main droite sur la touche &lt;b&gt;H&lt;/b&gt;.&lt;br&gt;Gardez vos doigts dans cette position et bougez le moins possible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;membre gauche&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;G&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;membre droit&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;H&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Después de cada ensayo recibirá una breve retroalimentación sobre su respuesta:&lt;br&gt;&lt;br&gt;Si ha respondido correctamente, la casilla correspondiente se iluminará &lt;span style='color:green'&gt;&lt;b&gt;verde&lt;/span&gt;&lt;/b&gt;.&lt;br&gt;&lt;br&gt;Si ha respondido incorrectamente, la casilla correspondiente se iluminará &lt;span style='color:red'&gt;&lt;b&gt;rojo&lt;/span&gt;&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Après chaque essai, vous recevrez un bref retour concernant votre réponse :&lt;br&gt;&lt;br&gt;Si vous avez répondu correctement, la case correspondante s'allumera en &lt;span style='color:green'&gt;&lt;b&gt;vert&lt;/span&gt;&lt;/b&gt;.&lt;br&gt;&lt;br&gt;Si vous avez répondu incorrectement, la case correspondante s'allumera en &lt;span style='color:red'&gt;&lt;b&gt;rouge&lt;/span&gt;&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>A continuación siguen algunos &lt;b&gt;ensayos de práctica&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Quelques &lt;b&gt;essais d'entraînement&lt;/b&gt; suivent maintenant.</t>
+  </si>
+  <si>
+    <t>Este es el final de los ensayos de práctica.</t>
+  </si>
+  <si>
+    <t>Ceci est la fin des essais d'entraînement.</t>
+  </si>
+  <si>
+    <t>Los estímulos que siguen a continuación se le presentarán &lt;b&gt;parcialmente rotados&lt;/b&gt;. Esto no debe influir en su&lt;br&gt;decisión. Debe juzgar exclusivamente si se trata de un miembro derecho o izquierdo.&lt;br&gt;&lt;br&gt;Decida por favor tan &lt;b&gt;rápido y correctamente&lt;/b&gt; como sea posible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;miembro izquierdo&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;S&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;miembro derecho&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;L&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Les stimuli qui vont suivre vous seront présentés &lt;b&gt;partiellement tournés&lt;/b&gt;. Cela ne doit avoir aucune influence sur votre&lt;br&gt;décision. Vous devez juger exclusivement s'il s'agit d'un membre droit ou gauche.&lt;br&gt;&lt;br&gt;Veuillez décider aussi &lt;b&gt;rapidement et correctement&lt;/b&gt; que possible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;membre gauche&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;S&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;membre droit&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;L&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Los estímulos que siguen a continuación se le presentarán &lt;b&gt;parcialmente rotados&lt;/b&gt;. Esto no debe influir en su&lt;br&gt;decisión. Debe juzgar exclusivamente si se trata de un miembro derecho o izquierdo.&lt;br&gt;&lt;br&gt;Decida por favor tan &lt;b&gt;rápido y correctamente&lt;/b&gt; como sea posible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;miembro izquierdo&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;G&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;miembro derecho&lt;/b&gt; (brazo o pierna) está apartado del cuerpo, pulse por favor la tecla &lt;b&gt;H&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Les stimuli qui vont suivre vous seront présentés &lt;b&gt;partiellement tournés&lt;/b&gt;. Cela ne doit avoir aucune influence sur votre&lt;br&gt;décision. Vous devez juger exclusivement s'il s'agit d'un membre droit ou gauche.&lt;br&gt;&lt;br&gt;Veuillez décider aussi &lt;b&gt;rapidement et correctement&lt;/b&gt; que possible.&lt;br&gt;&lt;br&gt;Si un &lt;b&gt;membre gauche&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;G&lt;/b&gt;.&lt;br&gt;Si un &lt;b&gt;membre droit&lt;/b&gt; (bras ou jambe) est écarté du corps, veuillez appuyer sur la touche &lt;b&gt;H&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>No recibirá ninguna retroalimentación.</t>
+  </si>
+  <si>
+    <t>Vous ne recevrez aucun retour.</t>
+  </si>
+  <si>
+    <t>Dies ist das Ende der Übungsdurchgänge.</t>
   </si>
 </sst>
 </file>
@@ -201,9 +268,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -241,7 +308,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -347,7 +414,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -489,7 +556,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -497,16 +564,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D84571D-E185-45F8-BE88-DC2A982E2C1F}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" customWidth="1"/>
-    <col min="2" max="3" width="100.7109375" customWidth="1"/>
+    <col min="1" max="1" width="21.875" customWidth="1"/>
+    <col min="2" max="5" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -514,63 +581,99 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="199.7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" ht="250.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="1" customFormat="1" ht="199.7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="1" customFormat="1" ht="199.7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" ht="85.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="1" customFormat="1" ht="282.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="1" customFormat="1" ht="282.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -580,52 +683,82 @@
       <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="168.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="114.15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="128.4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="1" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
